--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w5_0s_h5_0s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w5_0s_h5_0s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="29">
   <si>
     <t>event</t>
   </si>
@@ -112,6 +118,9 @@
   </si>
   <si>
     <t>horn(0-120), engine(120-240)</t>
+  </si>
+  <si>
+    <t>tire_squeal(0-120), impact(120-240)</t>
   </si>
 </sst>
 </file>
@@ -871,6 +880,182 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -915,6 +1100,94 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
